--- a/data/stats/supp_tables/fallcover-cc-ccwea-pairs.xlsx
+++ b/data/stats/supp_tables/fallcover-cc-ccwea-pairs.xlsx
@@ -351,56 +351,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>cctrt1</t>
+          <t>contrast</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>w1</t>
+          <t>weayear</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>cctrt2</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>w2</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>estimate</t>
+          <t>df</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>z.ratio</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>df</t>
+          <t>p.value</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>z.ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>p.value</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>psimp</t>
         </is>
@@ -409,7 +399,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mix_E</t>
+          <t>mix_E - mix_M</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -417,41 +407,31 @@
           <t>Y2018</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>mix_E</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Y2019</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>-2.09375678136051</v>
+      <c r="C2">
+        <v>1.760475692488603</v>
+      </c>
+      <c r="D2">
+        <v>0.1645998256543129</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="F2">
-        <v>0.1162492558416792</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>10.69548941191406</v>
+      </c>
+      <c r="G2">
+        <v>4.740652315149418E-14</v>
       </c>
       <c r="H2">
-        <v>-18.0109263169135</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mix_M</t>
+          <t>mix_E - nocc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -459,41 +439,31 @@
           <t>Y2018</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>mix_M</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Y2019</t>
-        </is>
-      </c>
-      <c r="E3">
-        <v>-2.193356617621231</v>
+      <c r="C3">
+        <v>1.982502435664745</v>
+      </c>
+      <c r="D3">
+        <v>0.1661713190482507</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="F3">
-        <v>0.1441393525034143</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>11.93047300231812</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>-15.21691737562977</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>rad_M</t>
+          <t>mix_E - rad_L</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -501,41 +471,31 @@
           <t>Y2018</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>rad_M</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Y2019</t>
-        </is>
-      </c>
-      <c r="E4">
-        <v>0.4037561133097465</v>
+      <c r="C4">
+        <v>-0.8049309776087988</v>
+      </c>
+      <c r="D4">
+        <v>0.1362453825422704</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="F4">
-        <v>0.09591941472246591</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>-5.907950512444469</v>
+      </c>
+      <c r="G4">
+        <v>3.458957908986093E-08</v>
       </c>
       <c r="H4">
-        <v>4.20932628162899</v>
-      </c>
-      <c r="I4">
-        <v>0.001064237470302931</v>
-      </c>
-      <c r="J4">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nocc</t>
+          <t>mix_E - rad_M</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -543,41 +503,31 @@
           <t>Y2018</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>nocc</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Y2019</t>
-        </is>
-      </c>
-      <c r="E5">
-        <v>-0.5699634689070362</v>
+      <c r="C5">
+        <v>-2.013433198313577</v>
+      </c>
+      <c r="D5">
+        <v>0.1337434742328431</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="F5">
-        <v>0.1616792555900941</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>-15.05444067355581</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>-3.525272718672495</v>
-      </c>
-      <c r="I5">
-        <v>0.01540051897591999</v>
-      </c>
-      <c r="J5">
-        <v>0.015</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rad_L</t>
+          <t>mix_M - nocc</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -585,35 +535,505 @@
           <t>Y2018</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>rad_L</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="C6">
+        <v>0.2220267431761427</v>
+      </c>
+      <c r="D6">
+        <v>0.1769085119743753</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="F6">
+        <v>1.255037084978154</v>
+      </c>
+      <c r="G6">
+        <v>0.7188135392371803</v>
+      </c>
+      <c r="H6">
+        <v>0.719</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mix_M - rad_L</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Y2018</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>-2.565406670097401</v>
+      </c>
+      <c r="D7">
+        <v>0.1567909163827704</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="F7">
+        <v>-16.36195979513588</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>mix_M - rad_M</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Y2018</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>-3.773908890802179</v>
+      </c>
+      <c r="D8">
+        <v>0.1560032709961646</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="F8">
+        <v>-24.19121641939778</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>nocc - rad_L</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Y2018</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>-2.787433413273544</v>
+      </c>
+      <c r="D9">
+        <v>0.158509827498132</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="F9">
+        <v>-17.58524034294588</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>nocc - rad_M</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Y2018</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>-3.995935633978322</v>
+      </c>
+      <c r="D10">
+        <v>0.1578392181754358</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="F10">
+        <v>-25.31649408917436</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>rad_L - rad_M</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Y2018</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>-1.208502220704778</v>
+      </c>
+      <c r="D11">
+        <v>0.1206589687125841</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="F11">
+        <v>-10.01585073699322</v>
+      </c>
+      <c r="G11">
+        <v>3.83026943495679E-14</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>mix_E - mix_M</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>Y2019</t>
         </is>
       </c>
-      <c r="E6">
-        <v>0.177194702552495</v>
-      </c>
-      <c r="F6">
-        <v>0.1068885855733672</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="H6">
-        <v>1.657751401629975</v>
-      </c>
-      <c r="I6">
-        <v>0.8191696403754143</v>
-      </c>
-      <c r="J6">
-        <v>0.819</v>
+      <c r="C12">
+        <v>1.660875856227882</v>
+      </c>
+      <c r="D12">
+        <v>0.1251086183079024</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="F12">
+        <v>13.27547117609702</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mix_E - nocc</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Y2019</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>3.506295748118219</v>
+      </c>
+      <c r="D13">
+        <v>0.1525145896109667</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="F13">
+        <v>22.98990383190263</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>mix_E - rad_L</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Y2019</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>1.466020506304206</v>
+      </c>
+      <c r="D14">
+        <v>0.1235498713371397</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="F14">
+        <v>11.86581977332673</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>mix_E - rad_M</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Y2019</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>0.4840796963566799</v>
+      </c>
+      <c r="D15">
+        <v>0.1172934639894427</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="F15">
+        <v>4.127081594250219</v>
+      </c>
+      <c r="G15">
+        <v>0.0003541612564019747</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>mix_M - nocc</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Y2019</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>1.845419891890337</v>
+      </c>
+      <c r="D16">
+        <v>0.1548659606827482</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="F16">
+        <v>11.9162395903822</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>mix_M - rad_L</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Y2019</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>-0.1948553499236758</v>
+      </c>
+      <c r="D17">
+        <v>0.1286456301893642</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="F17">
+        <v>-1.514667460036164</v>
+      </c>
+      <c r="G17">
+        <v>0.5528519499131284</v>
+      </c>
+      <c r="H17">
+        <v>0.553</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>mix_M - rad_M</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Y2019</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>-1.176796159871202</v>
+      </c>
+      <c r="D18">
+        <v>0.1236745945278487</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="F18">
+        <v>-9.515261920719013</v>
+      </c>
+      <c r="G18">
+        <v>4.141131881851834E-14</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>nocc - rad_L</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Y2019</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>-2.040275241814013</v>
+      </c>
+      <c r="D19">
+        <v>0.153767882031575</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="F19">
+        <v>-13.26853966418721</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>nocc - rad_M</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Y2019</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>-3.022216051761539</v>
+      </c>
+      <c r="D20">
+        <v>0.150848900067603</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="F20">
+        <v>-20.0347238223622</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>rad_L - rad_M</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Y2019</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>-0.9819408099475263</v>
+      </c>
+      <c r="D21">
+        <v>0.122063158780493</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="F21">
+        <v>-8.04453055088765</v>
+      </c>
+      <c r="G21">
+        <v>7.360778653264788E-14</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
